--- a/products-storage/00-free-uderzhaniya-do-podpisi/02-reestr-uderzhaniy-po-obektu.xlsx
+++ b/products-storage/00-free-uderzhaniya-do-podpisi/02-reestr-uderzhaniy-po-obektu.xlsx
@@ -970,35 +970,41 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="28" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Переход к платному комплекту</t>
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="36" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Комплект «Гарантийное удержание: возврат, оспаривание штрафов и зачётов» — 2 990 ₽.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
+          <t>Комплект «Система защиты подрядчика от претензий, штрафов, удержаний и зачётов» - 29 900 ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>https://marzhavbetone.ru/products/p5-shtrafy-uderzhaniya.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
+          <t>https://nastoronepodryadchika.ru/products/p5-shtrafy-uderzhaniya.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Комплект не заменяет юриста в споре по конкретному договору: он даёт формулировки и порядок, а оценку вашей позиции делает юрист.</t>
+          <t>Вопросы по комплекту: nastoronepodryadchika@yandex.ru</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A40:N40"/>
+    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="A42:N42"/>
+    <mergeCell ref="A43:N43"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>